--- a/artfynd/A 38044-2021 artfynd.xlsx
+++ b/artfynd/A 38044-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123132807</v>
+        <v>123132813</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>58156</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123132813</v>
+        <v>123132807</v>
       </c>
       <c r="B3" t="n">
-        <v>58156</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -815,14 +819,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">

--- a/artfynd/A 38044-2021 artfynd.xlsx
+++ b/artfynd/A 38044-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123132813</v>
+        <v>123132807</v>
       </c>
       <c r="B2" t="n">
-        <v>58156</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123132807</v>
+        <v>123132813</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>58156</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,10 +815,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">

--- a/artfynd/A 38044-2021 artfynd.xlsx
+++ b/artfynd/A 38044-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123132807</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>56694</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>123132813</v>
       </c>
       <c r="B3" t="n">
-        <v>58156</v>
+        <v>58159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 38044-2021 artfynd.xlsx
+++ b/artfynd/A 38044-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123132807</v>
+        <v>123132813</v>
       </c>
       <c r="B2" t="n">
-        <v>56694</v>
+        <v>58159</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123132813</v>
+        <v>123132807</v>
       </c>
       <c r="B3" t="n">
-        <v>58159</v>
+        <v>56694</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -815,14 +819,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">

--- a/artfynd/A 38044-2021 artfynd.xlsx
+++ b/artfynd/A 38044-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123132807</v>
       </c>
       <c r="B2" t="n">
-        <v>56694</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>123132813</v>
       </c>
       <c r="B3" t="n">
-        <v>58159</v>
+        <v>58165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 38044-2021 artfynd.xlsx
+++ b/artfynd/A 38044-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123132807</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>56703</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>123132813</v>
       </c>
       <c r="B3" t="n">
-        <v>58165</v>
+        <v>58168</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 38044-2021 artfynd.xlsx
+++ b/artfynd/A 38044-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123132807</v>
+        <v>123132813</v>
       </c>
       <c r="B2" t="n">
-        <v>56703</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123132813</v>
+        <v>123132807</v>
       </c>
       <c r="B3" t="n">
-        <v>58168</v>
+        <v>56703</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -815,14 +819,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
